--- a/gunnison_ami_listings.xlsx
+++ b/gunnison_ami_listings.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="114">
   <si>
     <t xml:space="preserve">Gunnison County, CO — HUD Area Median Income Limits (FY2024)</t>
   </si>
@@ -140,6 +140,24 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">County Residency Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">County Employment Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First-Time Buyer Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly Rent ($)</t>
+  </si>
+  <si>
     <t xml:space="preserve">GC-001</t>
   </si>
   <si>
@@ -158,6 +176,21 @@
     <t xml:space="preserve">Near downtown, deed-restricted</t>
   </si>
   <si>
+    <t xml:space="preserve">Ownership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
     <t xml:space="preserve">GC-002</t>
   </si>
   <si>
@@ -188,6 +221,9 @@
     <t xml:space="preserve">Ski-in access, HOA $320/mo</t>
   </si>
   <si>
+    <t xml:space="preserve">Pending</t>
+  </si>
+  <si>
     <t xml:space="preserve">GC-004</t>
   </si>
   <si>
@@ -222,6 +258,9 @@
   </si>
   <si>
     <t xml:space="preserve">Investor-owned, income restricted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rental</t>
   </si>
   <si>
     <t xml:space="preserve">GC-007</t>
@@ -330,10 +369,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="\$#,##0"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -477,8 +517,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -486,7 +530,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -522,20 +566,28 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -793,292 +845,292 @@
   <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="7" t="n">
         <v>19800</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>22700</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>25500</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>28300</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>30600</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>32900</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>35100</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="7" t="n">
         <v>37400</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="10" t="n">
         <v>33000</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="10" t="n">
         <v>37800</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="10" t="n">
         <v>42500</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <v>47200</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="10" t="n">
         <v>51000</v>
       </c>
-      <c r="H5" s="9" t="n">
+      <c r="H5" s="10" t="n">
         <v>54800</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="10" t="n">
         <v>58500</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J5" s="10" t="n">
         <v>62300</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>39600</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>45300</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>51000</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>56600</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>61200</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>65700</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="7" t="n">
         <v>70200</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="7" t="n">
         <v>74800</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="10" t="n">
         <v>52900</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <v>60400</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <v>68000</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>75500</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="10" t="n">
         <v>81600</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="10" t="n">
         <v>87600</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="10" t="n">
         <v>93600</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="10" t="n">
         <v>99700</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>66100</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <v>75500</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>85000</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>94400</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="7" t="n">
         <v>102000</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="7" t="n">
         <v>109500</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="7" t="n">
         <v>117100</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="7" t="n">
         <v>124600</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <v>79300</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="10" t="n">
         <v>90600</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="10" t="n">
         <v>102000</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <v>113300</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="10" t="n">
         <v>122300</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="10" t="n">
         <v>131400</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="10" t="n">
         <v>140500</v>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J9" s="10" t="n">
         <v>149500</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="7" t="n">
         <v>99100</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <v>113300</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>127400</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <v>141600</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="7" t="n">
         <v>152900</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="7" t="n">
         <v>164300</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="7" t="n">
         <v>175600</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="7" t="n">
         <v>186900</v>
       </c>
     </row>
@@ -1102,723 +1154,1017 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="11" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="O2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="P2" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="Q2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="R2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="S2" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="6" t="n">
         <v>1480</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="7" t="n">
         <v>385000</v>
       </c>
-      <c r="J3" s="12" t="n">
+      <c r="J3" s="13" t="n">
         <f aca="false">IF(H3&gt;0,I3/H3,"-")</f>
         <v>260.135135135135</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="11" t="str">
+      <c r="L3" s="12" t="str">
         <f aca="false">IF(K3="N/A","N/A",IF(VALUE(SUBSTITUTE(K3,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
-      <c r="M3" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="13" t="s">
+      <c r="M3" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="D4" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="9" t="n">
         <v>980</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I4" s="10" t="n">
         <v>298000</v>
       </c>
-      <c r="J4" s="14" t="n">
+      <c r="J4" s="15" t="n">
         <f aca="false">IF(H4&gt;0,I4/H4,"-")</f>
         <v>304.081632653061</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="13" t="str">
+      <c r="L4" s="14" t="str">
         <f aca="false">IF(K4="N/A","N/A",IF(VALUE(SUBSTITUTE(K4,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
-      <c r="M4" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="M4" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N4" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="O4" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="5" t="n">
+      <c r="P4" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="6" t="n">
         <v>640</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>425000</v>
       </c>
-      <c r="J5" s="12" t="n">
+      <c r="J5" s="13" t="n">
         <f aca="false">IF(H5&gt;0,I5/H5,"-")</f>
         <v>664.0625</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="11" t="str">
+      <c r="L5" s="12" t="str">
         <f aca="false">IF(K5="N/A","N/A",IF(VALUE(SUBSTITUTE(K5,"%",""))&lt;=80,"Yes","No"))</f>
         <v>No</v>
       </c>
-      <c r="M5" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="M5" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="S5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="8" t="n">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="9" t="n">
         <v>2200</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="10" t="n">
         <v>895000</v>
       </c>
-      <c r="J6" s="14" t="n">
+      <c r="J6" s="15" t="n">
         <f aca="false">IF(H6&gt;0,I6/H6,"-")</f>
         <v>406.818181818182</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="13" t="str">
+      <c r="L6" s="14" t="str">
         <f aca="false">IF(K6="N/A","N/A",IF(VALUE(SUBSTITUTE(K6,"%",""))&lt;=80,"Yes","No"))</f>
         <v>No</v>
       </c>
-      <c r="M6" s="13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F7" s="5" t="n">
+      <c r="M6" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="R6" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="7" t="n">
         <v>215000</v>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J7" s="13" t="n">
         <f aca="false">IF(H7&gt;0,I7/H7,"-")</f>
         <v>179.166666666667</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="11" t="str">
+      <c r="L7" s="12" t="str">
         <f aca="false">IF(K7="N/A","N/A",IF(VALUE(SUBSTITUTE(K7,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
-      <c r="M7" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="M7" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="9" t="n">
         <v>820</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="10" t="n">
         <v>249000</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="15" t="n">
         <f aca="false">IF(H8&gt;0,I8/H8,"-")</f>
         <v>303.658536585366</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="K8" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="13" t="str">
+      <c r="L8" s="14" t="str">
         <f aca="false">IF(K8="N/A","N/A",IF(VALUE(SUBSTITUTE(K8,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
-      <c r="M8" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="11" t="s">
+      <c r="M8" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="O8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="5" t="n">
+      <c r="P8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="R8" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="S8" s="16" t="n">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="6" t="n">
         <v>1750</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="7" t="n">
         <v>760000</v>
       </c>
-      <c r="J9" s="12" t="n">
+      <c r="J9" s="13" t="n">
         <f aca="false">IF(H9&gt;0,I9/H9,"-")</f>
         <v>434.285714285714</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="11" t="str">
+      <c r="L9" s="12" t="str">
         <f aca="false">IF(K9="N/A","N/A",IF(VALUE(SUBSTITUTE(K9,"%",""))&lt;=80,"Yes","No"))</f>
         <v>No</v>
       </c>
-      <c r="M9" s="11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" s="8" t="n">
+      <c r="M9" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S9" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="H10" s="9" t="n">
         <v>900</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="10" t="n">
         <v>272000</v>
       </c>
-      <c r="J10" s="14" t="n">
+      <c r="J10" s="15" t="n">
         <f aca="false">IF(H10&gt;0,I10/H10,"-")</f>
         <v>302.222222222222</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="13" t="str">
+      <c r="L10" s="14" t="str">
         <f aca="false">IF(K10="N/A","N/A",IF(VALUE(SUBSTITUTE(K10,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
-      <c r="M10" s="13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="5" t="n">
+      <c r="M10" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="6" t="n">
         <v>1900</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>468000</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="J11" s="13" t="n">
         <f aca="false">IF(H11&gt;0,I11/H11,"-")</f>
         <v>246.315789473684</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="L11" s="11" t="str">
+      <c r="L11" s="12" t="str">
         <f aca="false">IF(K11="N/A","N/A",IF(VALUE(SUBSTITUTE(K11,"%",""))&lt;=80,"Yes","No"))</f>
         <v>No</v>
       </c>
-      <c r="M11" s="11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="13" t="s">
+      <c r="M11" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="N11" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="8" t="n">
+      <c r="O11" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S11" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="9" t="n">
         <v>1050</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I12" s="10" t="n">
         <v>685000</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J12" s="15" t="n">
         <f aca="false">IF(H12&gt;0,I12/H12,"-")</f>
         <v>652.380952380952</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K12" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="L12" s="13" t="str">
+      <c r="L12" s="14" t="str">
         <f aca="false">IF(K12="N/A","N/A",IF(VALUE(SUBSTITUTE(K12,"%",""))&lt;=80,"Yes","No"))</f>
         <v>No</v>
       </c>
-      <c r="M12" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" s="11" t="s">
+      <c r="M12" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="N12" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="O12" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="R12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="6" t="n">
         <v>3.5</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="6" t="n">
         <v>3100</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="7" t="n">
         <v>1250000</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="J13" s="13" t="n">
         <f aca="false">IF(H13&gt;0,I13/H13,"-")</f>
         <v>403.225806451613</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="11" t="str">
+      <c r="L13" s="12" t="str">
         <f aca="false">IF(K13="N/A","N/A",IF(VALUE(SUBSTITUTE(K13,"%",""))&lt;=80,"Yes","No"))</f>
         <v>No</v>
       </c>
-      <c r="M13" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="13" t="s">
+      <c r="M13" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="R13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S13" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="D14" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="9" t="n">
         <v>1350</v>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I14" s="10" t="n">
         <v>340000</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J14" s="15" t="n">
         <f aca="false">IF(H14&gt;0,I14/H14,"-")</f>
         <v>251.851851851852</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="L14" s="13" t="str">
+      <c r="L14" s="14" t="str">
         <f aca="false">IF(K14="N/A","N/A",IF(VALUE(SUBSTITUTE(K14,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="5" t="n">
+      <c r="M14" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="6" t="n">
         <v>1050</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="7" t="n">
         <v>189000</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="J15" s="13" t="n">
         <f aca="false">IF(H15&gt;0,I15/H15,"-")</f>
         <v>180</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K15" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L15" s="11" t="str">
+      <c r="L15" s="12" t="str">
         <f aca="false">IF(K15="N/A","N/A",IF(VALUE(SUBSTITUTE(K15,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
-      <c r="M15" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="13" t="s">
+      <c r="M15" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="N15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="O15" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F16" s="8" t="n">
+      <c r="P15" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S15" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="G16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="8" t="n">
+      <c r="H16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I16" s="10" t="n">
         <v>320000</v>
       </c>
-      <c r="J16" s="14" t="str">
+      <c r="J16" s="15" t="str">
         <f aca="false">IF(H16&gt;0,I16/H16,"-")</f>
         <v>-</v>
       </c>
-      <c r="K16" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="L16" s="13" t="str">
+      <c r="K16" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="L16" s="14" t="str">
         <f aca="false">IF(K16="N/A","N/A",IF(VALUE(SUBSTITUTE(K16,"%",""))&lt;=80,"Yes","No"))</f>
         <v>N/A</v>
       </c>
-      <c r="M16" s="13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" s="5" t="n">
+      <c r="M16" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="R16" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H17" s="6" t="n">
         <v>1400</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="7" t="n">
         <v>165000</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="J17" s="13" t="n">
         <f aca="false">IF(H17&gt;0,I17/H17,"-")</f>
         <v>117.857142857143</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="L17" s="11" t="str">
+      <c r="L17" s="12" t="str">
         <f aca="false">IF(K17="N/A","N/A",IF(VALUE(SUBSTITUTE(K17,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
-      <c r="M17" s="11" t="s">
-        <v>100</v>
+      <c r="M17" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="R17" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S17" s="17" t="n">
+        <v>950</v>
       </c>
     </row>
   </sheetData>

--- a/gunnison_ami_listings.xlsx
+++ b/gunnison_ami_listings.xlsx
@@ -21,81 +21,111 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="114">
-  <si>
-    <t xml:space="preserve">Gunnison County, CO — HUD Area Median Income Limits (FY2024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: HUD FY2024 Income Limits — Gunnison County, CO. 4-person AMI = $94,400.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="124">
+  <si>
+    <t xml:space="preserve">Gunnison County, CO — 2026 Maximum Rents &amp; Income Limits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: Colorado Housing Finance Authority (CHFA) 2026 Income &amp; Rent Limits — Gunnison County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 Maximum Rents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 Income Limits</t>
   </si>
   <si>
     <t xml:space="preserve">AMI %</t>
   </si>
   <si>
-    <t xml:space="preserve">Income Limit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-Person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-Person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-Person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4-Person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-Person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6-Person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7-Person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8-Person</t>
+    <t xml:space="preserve">0 Bdrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Bdrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Bdrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Bdrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Bdrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 Person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 Person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40%</t>
   </si>
   <si>
     <t xml:space="preserve">30%</t>
   </si>
   <si>
-    <t xml:space="preserve">Extremely Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Very Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moderate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Above Moderate</t>
+    <t xml:space="preserve">20%</t>
   </si>
   <si>
     <t xml:space="preserve">Gunnison County, CO — Example Property Listings</t>
@@ -372,10 +402,10 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
-    <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="\$#,##0"/>
+    <numFmt numFmtId="166" formatCode="\$#,##0"/>
+    <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -416,6 +446,14 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
@@ -436,7 +474,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -452,7 +490,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E75B6"/>
-        <bgColor rgb="FF0066CC"/>
+        <bgColor rgb="FF4A90C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A90C4"/>
+        <bgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
     <fill>
@@ -517,12 +561,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -530,11 +570,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -542,51 +586,67 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -650,7 +710,7 @@
       <rgbColor rgb="FF595959"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF4A90C4"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -842,302 +902,868 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="7" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="J4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="K4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>3460</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>3710</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>4452</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>5146</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>5740</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>138400</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>158400</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>178080</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>197920</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>213760</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>229600</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>245440</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>261280</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>3243</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>3478</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>4173</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>4824</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>5381</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>129750</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>148500</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>166950</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>185550</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>200400</v>
+      </c>
+      <c r="L6" s="9" t="n">
+        <v>215250</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>230100</v>
+      </c>
+      <c r="N6" s="9" t="n">
+        <v>244950</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>3027</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>3246</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>3895</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>4502</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>5022</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>121100</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>138600</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>155820</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>173180</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>187040</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>200900</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>214760</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>228620</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>2811</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>3014</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>3617</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>4181</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>4663</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>112450</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>128700</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>144690</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>160810</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>173680</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>186550</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>199420</v>
+      </c>
+      <c r="N8" s="9" t="n">
+        <v>212290</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>2595</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>2782</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>3339</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>3859</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>4305</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>103800</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>118800</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>133560</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>148440</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>160320</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>172200</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>184080</v>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>195960</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>2378</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>2550</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>3060</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>3537</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>3946</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>95150</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>108900</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>122430</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>136070</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>146960</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>157850</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>168740</v>
+      </c>
+      <c r="N10" s="9" t="n">
+        <v>179630</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>2162</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>2318</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>2782</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>3216</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>3587</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>86500</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>99000</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>111300</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>123700</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>133600</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>143500</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>153400</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>163300</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>1946</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>2086</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>2504</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>2894</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>3228</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>77850</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>89100</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>100170</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>111330</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>120240</v>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>129150</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>138060</v>
+      </c>
+      <c r="N12" s="9" t="n">
+        <v>146970</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>1730</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>1855</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>2226</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>2573</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2870</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>69200</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>79200</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>89040</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>98960</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>106880</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>114800</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>122720</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>130640</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>1513</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>1623</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>1947</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>2251</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>2511</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>60550</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>69300</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>77910</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>86590</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>93520</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>100450</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>107380</v>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>114310</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>1391</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>1669</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>1929</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>2152</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>51900</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>59400</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>66780</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>74220</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>80160</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>86100</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>92040</v>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>97980</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>1189</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>1275</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1530</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>1768</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>1973</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>47575</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>54450</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>61215</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>68035</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>73480</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>78925</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>84370</v>
+      </c>
+      <c r="N16" s="9" t="n">
+        <v>89815</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>1081</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>1159</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>1391</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>1608</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>1793</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>43250</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>49500</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>55650</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>61850</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>66800</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>71750</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>76700</v>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>81650</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>973</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>1043</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>1252</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>1447</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>1614</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>38925</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>44550</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>50085</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>55665</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>60120</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>64575</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>69030</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>73485</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>865</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>927</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>1113</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>1286</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>1435</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>34600</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>39600</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>44520</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>49480</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>53440</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>57400</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>61360</v>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>65320</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>648</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>695</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>834</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>964</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>1076</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>25950</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>29700</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>33390</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>37110</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>40080</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>43050</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>46020</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>48990</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>432</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>463</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>556</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>643</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>717</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>17300</v>
+      </c>
+      <c r="H21" s="7" t="n">
         <v>19800</v>
       </c>
-      <c r="D4" s="7" t="n">
-        <v>22700</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>25500</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>28300</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>30600</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>32900</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>35100</v>
-      </c>
-      <c r="J4" s="7" t="n">
-        <v>37400</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>33000</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>37800</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>42500</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>47200</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>51000</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>54800</v>
-      </c>
-      <c r="I5" s="10" t="n">
-        <v>58500</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>62300</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>39600</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>45300</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>51000</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>56600</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>61200</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>65700</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>70200</v>
-      </c>
-      <c r="J6" s="7" t="n">
-        <v>74800</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>52900</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>60400</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>68000</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>75500</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>81600</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>87600</v>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>93600</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>99700</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>66100</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>75500</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>94400</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>102000</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>109500</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>117100</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>124600</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>79300</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>90600</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>102000</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>113300</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>122300</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>131400</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>140500</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>149500</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>99100</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>113300</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>127400</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>141600</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>152900</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>164300</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>175600</v>
-      </c>
-      <c r="J10" s="7" t="n">
-        <v>186900</v>
+      <c r="I21" s="7" t="n">
+        <v>22260</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>24740</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>26720</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>28700</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>30680</v>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>32660</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:N3"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1157,1013 +1783,1013 @@
   <dimension ref="A1:S17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="10" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="10" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="10" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="10" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="10" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="10" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="10" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="10" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="10" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="10" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="10" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="10" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="10" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="10" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="10" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="10" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="R2" s="11" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="S2" s="11" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F3" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="13" t="n">
         <v>1480</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I3" s="14" t="n">
         <v>385000</v>
       </c>
-      <c r="J3" s="13" t="n">
+      <c r="J3" s="15" t="n">
         <f aca="false">IF(H3&gt;0,I3/H3,"-")</f>
         <v>260.135135135135</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="L3" s="12" t="str">
         <f aca="false">IF(K3="N/A","N/A",IF(VALUE(SUBSTITUTE(K3,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>55</v>
+        <v>60</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q3" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="S3" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="A4" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="E4" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="H4" s="17" t="n">
         <v>980</v>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="I4" s="18" t="n">
         <v>298000</v>
       </c>
-      <c r="J4" s="15" t="n">
+      <c r="J4" s="19" t="n">
         <f aca="false">IF(H4&gt;0,I4/H4,"-")</f>
         <v>304.081632653061</v>
       </c>
-      <c r="K4" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" s="14" t="str">
+      <c r="K4" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="16" t="str">
         <f aca="false">IF(K4="N/A","N/A",IF(VALUE(SUBSTITUTE(K4,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
-      <c r="M4" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="S4" s="9" t="s">
-        <v>55</v>
+      <c r="M4" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="P4" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="R4" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="S4" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="F5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="13" t="n">
         <v>640</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="14" t="n">
         <v>425000</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="15" t="n">
         <f aca="false">IF(H5&gt;0,I5/H5,"-")</f>
         <v>664.0625</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L5" s="12" t="str">
         <f aca="false">IF(K5="N/A","N/A",IF(VALUE(SUBSTITUTE(K5,"%",""))&lt;=80,"Yes","No"))</f>
         <v>No</v>
       </c>
       <c r="M5" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="P5" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q5" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="S5" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="N5" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="9" t="n">
+      <c r="A6" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H6" s="17" t="n">
         <v>2200</v>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="I6" s="18" t="n">
         <v>895000</v>
       </c>
-      <c r="J6" s="15" t="n">
+      <c r="J6" s="19" t="n">
         <f aca="false">IF(H6&gt;0,I6/H6,"-")</f>
         <v>406.818181818182</v>
       </c>
-      <c r="K6" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="14" t="str">
+      <c r="K6" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="16" t="str">
         <f aca="false">IF(K6="N/A","N/A",IF(VALUE(SUBSTITUTE(K6,"%",""))&lt;=80,"Yes","No"))</f>
         <v>No</v>
       </c>
-      <c r="M6" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="P6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="R6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="S6" s="9" t="s">
-        <v>55</v>
+      <c r="M6" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="O6" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q6" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="R6" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="S6" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="F7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="13" t="n">
         <v>1200</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="14" t="n">
         <v>215000</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="15" t="n">
         <f aca="false">IF(H7&gt;0,I7/H7,"-")</f>
         <v>179.166666666667</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="L7" s="12" t="str">
         <f aca="false">IF(K7="N/A","N/A",IF(VALUE(SUBSTITUTE(K7,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q7" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="S7" s="6" t="s">
-        <v>55</v>
+        <v>85</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="P7" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q7" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="R7" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="S7" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" s="9" t="n">
+      <c r="A8" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H8" s="17" t="n">
         <v>820</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I8" s="18" t="n">
         <v>249000</v>
       </c>
-      <c r="J8" s="15" t="n">
+      <c r="J8" s="19" t="n">
         <f aca="false">IF(H8&gt;0,I8/H8,"-")</f>
         <v>303.658536585366</v>
       </c>
-      <c r="K8" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" s="14" t="str">
+      <c r="K8" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="16" t="str">
         <f aca="false">IF(K8="N/A","N/A",IF(VALUE(SUBSTITUTE(K8,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
-      <c r="M8" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="R8" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="S8" s="16" t="n">
+      <c r="M8" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="O8" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="P8" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q8" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="R8" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="S8" s="20" t="n">
         <v>1650</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F9" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="13" t="n">
         <v>2.5</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="13" t="n">
         <v>1750</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="14" t="n">
         <v>760000</v>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="J9" s="15" t="n">
         <f aca="false">IF(H9&gt;0,I9/H9,"-")</f>
         <v>434.285714285714</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L9" s="12" t="str">
         <f aca="false">IF(K9="N/A","N/A",IF(VALUE(SUBSTITUTE(K9,"%",""))&lt;=80,"Yes","No"))</f>
         <v>No</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="P9" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q9" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="R9" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="S9" s="6" t="s">
-        <v>55</v>
+        <v>92</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q9" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="R9" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="S9" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="9" t="n">
+      <c r="A10" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="17" t="n">
         <v>900</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I10" s="18" t="n">
         <v>272000</v>
       </c>
-      <c r="J10" s="15" t="n">
+      <c r="J10" s="19" t="n">
         <f aca="false">IF(H10&gt;0,I10/H10,"-")</f>
         <v>302.222222222222</v>
       </c>
-      <c r="K10" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="L10" s="14" t="str">
+      <c r="K10" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" s="16" t="str">
         <f aca="false">IF(K10="N/A","N/A",IF(VALUE(SUBSTITUTE(K10,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
-      <c r="M10" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="R10" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="S10" s="9" t="s">
-        <v>55</v>
+      <c r="M10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="O10" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="P10" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q10" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="R10" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="S10" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="13" t="n">
         <v>1900</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="14" t="n">
         <v>468000</v>
       </c>
-      <c r="J11" s="13" t="n">
+      <c r="J11" s="15" t="n">
         <f aca="false">IF(H11&gt;0,I11/H11,"-")</f>
         <v>246.315789473684</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L11" s="12" t="str">
         <f aca="false">IF(K11="N/A","N/A",IF(VALUE(SUBSTITUTE(K11,"%",""))&lt;=80,"Yes","No"))</f>
         <v>No</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="S11" s="6" t="s">
-        <v>55</v>
+        <v>99</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O11" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="P11" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q11" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="R11" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="S11" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="9" t="n">
+      <c r="A12" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H12" s="17" t="n">
         <v>1050</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I12" s="18" t="n">
         <v>685000</v>
       </c>
-      <c r="J12" s="15" t="n">
+      <c r="J12" s="19" t="n">
         <f aca="false">IF(H12&gt;0,I12/H12,"-")</f>
         <v>652.380952380952</v>
       </c>
-      <c r="K12" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="14" t="str">
+      <c r="K12" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="16" t="str">
         <f aca="false">IF(K12="N/A","N/A",IF(VALUE(SUBSTITUTE(K12,"%",""))&lt;=80,"Yes","No"))</f>
         <v>No</v>
       </c>
-      <c r="M12" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="R12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="S12" s="9" t="s">
-        <v>55</v>
+      <c r="M12" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="O12" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="P12" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q12" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="R12" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="S12" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F13" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="13" t="n">
         <v>3.5</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="13" t="n">
         <v>3100</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="14" t="n">
         <v>1250000</v>
       </c>
-      <c r="J13" s="13" t="n">
+      <c r="J13" s="15" t="n">
         <f aca="false">IF(H13&gt;0,I13/H13,"-")</f>
         <v>403.225806451613</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L13" s="12" t="str">
         <f aca="false">IF(K13="N/A","N/A",IF(VALUE(SUBSTITUTE(K13,"%",""))&lt;=80,"Yes","No"))</f>
         <v>No</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="S13" s="6" t="s">
-        <v>55</v>
+        <v>105</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="P13" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q13" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="R13" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="S13" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="14" t="s">
+      <c r="A14" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="E14" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="17" t="n">
         <v>2.5</v>
       </c>
-      <c r="H14" s="9" t="n">
+      <c r="H14" s="17" t="n">
         <v>1350</v>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="I14" s="18" t="n">
         <v>340000</v>
       </c>
-      <c r="J14" s="15" t="n">
+      <c r="J14" s="19" t="n">
         <f aca="false">IF(H14&gt;0,I14/H14,"-")</f>
         <v>251.851851851852</v>
       </c>
-      <c r="K14" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="L14" s="14" t="str">
+      <c r="K14" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="16" t="str">
         <f aca="false">IF(K14="N/A","N/A",IF(VALUE(SUBSTITUTE(K14,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
-      <c r="M14" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="P14" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q14" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="R14" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="S14" s="9" t="s">
-        <v>55</v>
+      <c r="M14" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="O14" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="P14" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q14" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="R14" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="S14" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="13" t="n">
         <v>1050</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I15" s="14" t="n">
         <v>189000</v>
       </c>
-      <c r="J15" s="13" t="n">
+      <c r="J15" s="15" t="n">
         <f aca="false">IF(H15&gt;0,I15/H15,"-")</f>
         <v>180</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="L15" s="12" t="str">
         <f aca="false">IF(K15="N/A","N/A",IF(VALUE(SUBSTITUTE(K15,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="O15" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="R15" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="S15" s="6" t="s">
-        <v>55</v>
+        <v>113</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q15" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="S15" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="F16" s="9" t="n">
+      <c r="A16" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="F16" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="9" t="n">
+      <c r="H16" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I16" s="18" t="n">
         <v>320000</v>
       </c>
-      <c r="J16" s="15" t="str">
+      <c r="J16" s="19" t="str">
         <f aca="false">IF(H16&gt;0,I16/H16,"-")</f>
         <v>-</v>
       </c>
-      <c r="K16" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="L16" s="14" t="str">
+      <c r="K16" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="L16" s="16" t="str">
         <f aca="false">IF(K16="N/A","N/A",IF(VALUE(SUBSTITUTE(K16,"%",""))&lt;=80,"Yes","No"))</f>
         <v>N/A</v>
       </c>
-      <c r="M16" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="P16" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q16" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="R16" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="S16" s="9" t="s">
-        <v>55</v>
+      <c r="M16" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="P16" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q16" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="R16" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="S16" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="F17" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="13" t="n">
         <v>1400</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="14" t="n">
         <v>165000</v>
       </c>
-      <c r="J17" s="13" t="n">
+      <c r="J17" s="15" t="n">
         <f aca="false">IF(H17&gt;0,I17/H17,"-")</f>
         <v>117.857142857143</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="L17" s="12" t="str">
         <f aca="false">IF(K17="N/A","N/A",IF(VALUE(SUBSTITUTE(K17,"%",""))&lt;=80,"Yes","No"))</f>
         <v>Yes</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="O17" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="P17" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q17" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="R17" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="S17" s="17" t="n">
+        <v>123</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="P17" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q17" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="R17" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="S17" s="21" t="n">
         <v>950</v>
       </c>
     </row>
